--- a/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
+++ b/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
+++ b/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
+++ b/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
+++ b/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>View</t>
+  </si>
+  <si>
+    <t>questionnairelinkage</t>
+  </si>
+  <si>
+    <t>Questionnaire linkage</t>
   </si>
 </sst>
 </file>
@@ -452,7 +458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -493,6 +499,18 @@
       </c>
       <c r="D3" s="2"/>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
+++ b/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
+++ b/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
+++ b/fhir/CodeSystem-ehealth-basic-resource-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
